--- a/Assets/Excel/Equipment/EquipmentData.xlsx
+++ b/Assets/Excel/Equipment/EquipmentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Assets\Excel\Equipment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA20C58E-F8EC-4E1A-885E-E2D1073185C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A4E1A2-F6F7-4B43-9A57-D7A9441F3FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -501,7 +501,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -513,7 +513,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
